--- a/tests/files/missing-first-round-title.xlsx
+++ b/tests/files/missing-first-round-title.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Tabelle2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
   <si>
     <t xml:space="preserve">28.11. Im vergangenen Monat wurde bekannt, dass die Lieblingsburgerkette von Barack Obama vor der Insolvenz steht. Am Freitag schloss dann die erste Filiale von Five Guys. Besser läuft es für eine Berliner Kultmarke, die vom Szene-Imbiss zum ernstzunehmenden Player wurde. Mit einem durchschnittlichen Umsatz von 3,25 Millionen Euro pro Standort setzt sich die Marke damit hinter McDonald’s auf Platz 2 der umsatzstärksten Standorte in der deutschen Systemgastronomie. Welche Kette suche ich?</t>
   </si>
@@ -296,86 +295,18 @@
   </si>
   <si>
     <t xml:space="preserve">Stratford-upon-Avon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Über 6000 Meter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicht über 6000 Meter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbrus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denali (6190)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mont Blanc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Aconcagua (6960)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cotopaxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monte Pissis (6793)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Misty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makalu (8463)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sliabh Ard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annapurna 1 (8091)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altas Montagnona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nanga Parbat (8125)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secret Peak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pico Veintimilla (6228)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pik Vysoka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island Peak (6189)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kastanjeblomst Tinde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hidden Peak (8068)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kibo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pik Pobeda (7439)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/\ mmm"/>
-    <numFmt numFmtId="167" formatCode="0\ %"/>
-    <numFmt numFmtId="168" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,74 +345,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <u val="single"/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <u val="single"/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF1B1E25"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -492,18 +357,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF33CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999"/>
-        <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -539,11 +392,9 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -592,78 +443,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,66 +452,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFA9D18E"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00B0F0"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1B1E25"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -744,37 +463,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -5877,259 +5596,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="80.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="43.14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12"/>
-      <c r="B1" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="16"/>
-    </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="4" customFormat="false" ht="36.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16"/>
-    </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="16"/>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-    </row>
-    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>